--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1479,6 +1479,353 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122829206</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Betlehem SSV 775 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577105</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6510694</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122832709</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Betlehem S 705 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577248</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6510738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122832809</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105453</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Betlehem SSV 850 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577099</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6510613</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Krokek</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>105461</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,42 +1497,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R9" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,6 +1573,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1599,7 +1600,7 @@
         <v>122832709</v>
       </c>
       <c r="B10" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1712,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B11" t="n">
-        <v>105453</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,42 +1729,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R11" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,7 +1805,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B9" t="n">
-        <v>105461</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,42 +1497,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R9" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1573,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1713,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>105461</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,42 +1728,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R11" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,6 +1804,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>105463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,42 +1497,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R9" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,6 +1573,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1599,7 +1600,7 @@
         <v>122832709</v>
       </c>
       <c r="B10" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1712,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B11" t="n">
-        <v>105461</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,42 +1729,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R11" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,7 +1805,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832709</v>
+        <v>122829206</v>
       </c>
       <c r="B10" t="n">
-        <v>105463</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,45 +1613,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem S 705 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577248</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>6510738</v>
+        <v>6510694</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,7 +1689,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1713,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122829206</v>
+        <v>122832709</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>105463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,45 +1728,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577105</v>
+        <v>577248</v>
       </c>
       <c r="R11" t="n">
-        <v>6510694</v>
+        <v>6510738</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1805,6 +1804,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B9" t="n">
-        <v>105463</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,42 +1497,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R9" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1573,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>105471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,42 +1612,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R10" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,6 +1688,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>122832709</v>
       </c>
       <c r="B11" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>105471</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1497,42 +1497,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R9" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,6 +1573,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1596,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,42 +1613,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1688,7 +1689,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1481,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122832809</v>
+        <v>122832709</v>
       </c>
       <c r="B9" t="n">
         <v>105471</v>
@@ -1525,17 +1525,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem S 705 m, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577099</v>
+        <v>577248</v>
       </c>
       <c r="R9" t="n">
-        <v>6510613</v>
+        <v>6510738</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>105471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,42 +1613,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R10" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,6 +1689,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1712,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122832709</v>
+        <v>122829206</v>
       </c>
       <c r="B11" t="n">
-        <v>105471</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,45 +1729,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem S 705 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577248</v>
+        <v>577105</v>
       </c>
       <c r="R11" t="n">
-        <v>6510738</v>
+        <v>6510694</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1804,7 +1805,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>122832709</v>
       </c>
       <c r="B9" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,42 +1613,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,7 +1689,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1713,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>105474</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,42 +1728,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R11" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,6 +1804,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>122832709</v>
       </c>
       <c r="B9" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B10" t="n">
-        <v>56691</v>
+        <v>105476</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,42 +1613,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R10" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,6 +1689,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1712,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B11" t="n">
-        <v>105474</v>
+        <v>56691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,42 +1729,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R11" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1804,7 +1805,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>122832709</v>
       </c>
       <c r="B9" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832809</v>
+        <v>122829206</v>
       </c>
       <c r="B10" t="n">
-        <v>105476</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,42 +1613,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Betlehem SSV 850 m, Ög</t>
+          <t>Betlehem SSV 775 m, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577099</v>
+        <v>577105</v>
       </c>
       <c r="R10" t="n">
-        <v>6510613</v>
+        <v>6510694</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,7 +1689,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1713,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122829206</v>
+        <v>122832809</v>
       </c>
       <c r="B11" t="n">
-        <v>56691</v>
+        <v>105482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,42 +1728,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Betlehem SSV 775 m, Ög</t>
+          <t>Betlehem SSV 850 m, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577105</v>
+        <v>577099</v>
       </c>
       <c r="R11" t="n">
-        <v>6510694</v>
+        <v>6510613</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1805,6 +1804,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>122829206</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 4446-2025 artfynd.xlsx
+++ b/artfynd/A 4446-2025 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>122829206</v>
       </c>
       <c r="B9" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
